--- a/momentum_sharpe_summary.xlsx
+++ b/momentum_sharpe_summary.xlsx
@@ -573,7 +573,7 @@
         <v>0.975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.362</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>-0.286</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.158</v>
+        <v>-0.166</v>
       </c>
     </row>
     <row r="12">
@@ -645,7 +645,7 @@
         <v>-0.422</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.013</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="13">
